--- a/Дело3а-78-2026Таганай/01_Иск/01.11_Комплект_Для_суда/Для суда от Виктории/Для СУДА/28. Сотрудники/2025 год/Кульбатырова- диспетчер/Сводная_ведомость.xlsx
+++ b/Дело3а-78-2026Таганай/01_Иск/01.11_Комплект_Для_суда/Для суда от Виктории/Для СУДА/28. Сотрудники/2025 год/Кульбатырова- диспетчер/Сводная_ведомость.xlsx
@@ -651,7 +651,7 @@
         </is>
       </c>
       <c r="I6" s="7" t="n">
-        <v>46157.92574739858</v>
+        <v>46157.93118668826</v>
       </c>
     </row>
     <row r="7" ht="15" customHeight="1">

--- a/Дело3а-78-2026Таганай/01_Иск/01.11_Комплект_Для_суда/Для суда от Виктории/Для СУДА/28. Сотрудники/2025 год/Кульбатырова- диспетчер/Сводная_ведомость.xlsx
+++ b/Дело3а-78-2026Таганай/01_Иск/01.11_Комплект_Для_суда/Для суда от Виктории/Для СУДА/28. Сотрудники/2025 год/Кульбатырова- диспетчер/Сводная_ведомость.xlsx
@@ -651,7 +651,7 @@
         </is>
       </c>
       <c r="I6" s="7" t="n">
-        <v>46157.93118668826</v>
+        <v>46157.93184052477</v>
       </c>
     </row>
     <row r="7" ht="15" customHeight="1">

--- a/Дело3а-78-2026Таганай/01_Иск/01.11_Комплект_Для_суда/Для суда от Виктории/Для СУДА/28. Сотрудники/2025 год/Кульбатырова- диспетчер/Сводная_ведомость.xlsx
+++ b/Дело3а-78-2026Таганай/01_Иск/01.11_Комплект_Для_суда/Для суда от Виктории/Для СУДА/28. Сотрудники/2025 год/Кульбатырова- диспетчер/Сводная_ведомость.xlsx
@@ -651,7 +651,7 @@
         </is>
       </c>
       <c r="I6" s="7" t="n">
-        <v>46157.93184052477</v>
+        <v>46157.93406058804</v>
       </c>
     </row>
     <row r="7" ht="15" customHeight="1">

--- a/Дело3а-78-2026Таганай/01_Иск/01.11_Комплект_Для_суда/Для суда от Виктории/Для СУДА/28. Сотрудники/2025 год/Кульбатырова- диспетчер/Сводная_ведомость.xlsx
+++ b/Дело3а-78-2026Таганай/01_Иск/01.11_Комплект_Для_суда/Для суда от Виктории/Для СУДА/28. Сотрудники/2025 год/Кульбатырова- диспетчер/Сводная_ведомость.xlsx
@@ -651,7 +651,7 @@
         </is>
       </c>
       <c r="I6" s="7" t="n">
-        <v>46157.93406058804</v>
+        <v>46157.9372410518</v>
       </c>
     </row>
     <row r="7" ht="15" customHeight="1">

--- a/Дело3а-78-2026Таганай/01_Иск/01.11_Комплект_Для_суда/Для суда от Виктории/Для СУДА/28. Сотрудники/2025 год/Кульбатырова- диспетчер/Сводная_ведомость.xlsx
+++ b/Дело3а-78-2026Таганай/01_Иск/01.11_Комплект_Для_суда/Для суда от Виктории/Для СУДА/28. Сотрудники/2025 год/Кульбатырова- диспетчер/Сводная_ведомость.xlsx
@@ -651,7 +651,7 @@
         </is>
       </c>
       <c r="I6" s="7" t="n">
-        <v>46157.9372410518</v>
+        <v>46158.28221902218</v>
       </c>
     </row>
     <row r="7" ht="15" customHeight="1">

--- a/Дело3а-78-2026Таганай/01_Иск/01.11_Комплект_Для_суда/Для суда от Виктории/Для СУДА/28. Сотрудники/2025 год/Кульбатырова- диспетчер/Сводная_ведомость.xlsx
+++ b/Дело3а-78-2026Таганай/01_Иск/01.11_Комплект_Для_суда/Для суда от Виктории/Для СУДА/28. Сотрудники/2025 год/Кульбатырова- диспетчер/Сводная_ведомость.xlsx
@@ -651,7 +651,7 @@
         </is>
       </c>
       <c r="I6" s="7" t="n">
-        <v>46158.28221902218</v>
+        <v>46158.29702873881</v>
       </c>
     </row>
     <row r="7" ht="15" customHeight="1">

--- a/Дело3а-78-2026Таганай/01_Иск/01.11_Комплект_Для_суда/Для суда от Виктории/Для СУДА/28. Сотрудники/2025 год/Кульбатырова- диспетчер/Сводная_ведомость.xlsx
+++ b/Дело3а-78-2026Таганай/01_Иск/01.11_Комплект_Для_суда/Для суда от Виктории/Для СУДА/28. Сотрудники/2025 год/Кульбатырова- диспетчер/Сводная_ведомость.xlsx
@@ -651,7 +651,7 @@
         </is>
       </c>
       <c r="I6" s="7" t="n">
-        <v>46158.29702873881</v>
+        <v>46158.29821702712</v>
       </c>
     </row>
     <row r="7" ht="15" customHeight="1">

--- a/Дело3а-78-2026Таганай/01_Иск/01.11_Комплект_Для_суда/Для суда от Виктории/Для СУДА/28. Сотрудники/2025 год/Кульбатырова- диспетчер/Сводная_ведомость.xlsx
+++ b/Дело3а-78-2026Таганай/01_Иск/01.11_Комплект_Для_суда/Для суда от Виктории/Для СУДА/28. Сотрудники/2025 год/Кульбатырова- диспетчер/Сводная_ведомость.xlsx
@@ -651,7 +651,7 @@
         </is>
       </c>
       <c r="I6" s="7" t="n">
-        <v>46158.29821702712</v>
+        <v>46158.33392864649</v>
       </c>
     </row>
     <row r="7" ht="15" customHeight="1">

--- a/Дело3а-78-2026Таганай/01_Иск/01.11_Комплект_Для_суда/Для суда от Виктории/Для СУДА/28. Сотрудники/2025 год/Кульбатырова- диспетчер/Сводная_ведомость.xlsx
+++ b/Дело3а-78-2026Таганай/01_Иск/01.11_Комплект_Для_суда/Для суда от Виктории/Для СУДА/28. Сотрудники/2025 год/Кульбатырова- диспетчер/Сводная_ведомость.xlsx
@@ -651,7 +651,7 @@
         </is>
       </c>
       <c r="I6" s="7" t="n">
-        <v>46158.33392864649</v>
+        <v>46158.36862653333</v>
       </c>
     </row>
     <row r="7" ht="15" customHeight="1">

--- a/Дело3а-78-2026Таганай/01_Иск/01.11_Комплект_Для_суда/Для суда от Виктории/Для СУДА/28. Сотрудники/2025 год/Кульбатырова- диспетчер/Сводная_ведомость.xlsx
+++ b/Дело3а-78-2026Таганай/01_Иск/01.11_Комплект_Для_суда/Для суда от Виктории/Для СУДА/28. Сотрудники/2025 год/Кульбатырова- диспетчер/Сводная_ведомость.xlsx
@@ -651,7 +651,7 @@
         </is>
       </c>
       <c r="I6" s="7" t="n">
-        <v>46158.36862653333</v>
+        <v>46158.37293618278</v>
       </c>
     </row>
     <row r="7" ht="15" customHeight="1">
